--- a/artfynd/A 58223-2021 artfynd.xlsx
+++ b/artfynd/A 58223-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58223-2021 artfynd.xlsx
+++ b/artfynd/A 58223-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96785766</v>
+        <v>96785755</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407339.4663186476</v>
+        <v>406690</v>
       </c>
       <c r="R2" t="n">
-        <v>7083646.478051158</v>
+        <v>7083362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,12 +763,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i gammal granskog på frisk mark</t>
+          <t>i gammal granskog intill å</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>på bark på död rönn ca 25 cm i diameter</t>
+          <t>på kvistar på levande gran</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -806,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96785759</v>
+        <v>96785760</v>
       </c>
       <c r="B3" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406839.6152487522</v>
+        <v>407040</v>
       </c>
       <c r="R3" t="n">
-        <v>7083473.367485152</v>
+        <v>7083507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,12 +879,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>i gammal granskog intill å</t>
+          <t>i gammal granskog på frisk mark</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ppå bark på död kvist på levande gran ca 25 cm i diameter</t>
+          <t>på högstubbe av björk ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -937,32 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96785758</v>
+        <v>96785762</v>
       </c>
       <c r="B4" t="n">
-        <v>77960</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6038705</v>
+        <v>308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -975,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406690.0686645505</v>
+        <v>407277</v>
       </c>
       <c r="R4" t="n">
-        <v>7083361.348371542</v>
+        <v>7083681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,19 +978,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,12 +995,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>i gammal granskog intill å</t>
+          <t>i gransumpskog nära bäck</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>på kvistar på levande gran</t>
+          <t>på ved på högstubbe av björk ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1066,12 +1026,7 @@
         <v>96785764</v>
       </c>
       <c r="B5" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407331.1595124583</v>
+        <v>407331</v>
       </c>
       <c r="R5" t="n">
-        <v>7083649.370339864</v>
+        <v>7083650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,19 +1094,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96785771</v>
+        <v>96785759</v>
       </c>
       <c r="B6" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1249</v>
+        <v>498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1237,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407432.5825721307</v>
+        <v>406839</v>
       </c>
       <c r="R6" t="n">
-        <v>7083628.728832532</v>
+        <v>7083474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1270,19 +1210,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,12 +1227,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>i ganska bördig gammal granskog 15 m från en bäck</t>
+          <t>i gammal granskog intill å</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>på gren på levande gammal dubbelgran ca 50 cm i diameter</t>
+          <t>ppå bark på död kvist på levande gran ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1325,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96785760</v>
+        <v>96785761</v>
       </c>
       <c r="B7" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1368,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407040.2771367845</v>
+        <v>407093</v>
       </c>
       <c r="R7" t="n">
-        <v>7083507.114428735</v>
+        <v>7083514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,19 +1326,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,7 +1348,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>på högstubbe av björk ca 30 cm i diameter</t>
+          <t>på granlåga ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1459,12 +1374,7 @@
         <v>96785756</v>
       </c>
       <c r="B8" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406690.0686645505</v>
+        <v>406690</v>
       </c>
       <c r="R8" t="n">
-        <v>7083361.348371542</v>
+        <v>7083362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1532,19 +1442,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1587,37 +1487,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96785755</v>
+        <v>96785771</v>
       </c>
       <c r="B9" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1630,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406690.0686645505</v>
+        <v>407432</v>
       </c>
       <c r="R9" t="n">
-        <v>7083361.348371542</v>
+        <v>7083629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1663,19 +1558,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,12 +1575,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>i gammal granskog intill å</t>
+          <t>i ganska bördig gammal granskog 15 m från en bäck</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>på kvistar på levande gran</t>
+          <t>på gren på levande gammal dubbelgran ca 50 cm i diameter</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1718,15 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96785761</v>
+        <v>96785763</v>
       </c>
       <c r="B10" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,21 +1614,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1761,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407093.0310834468</v>
+        <v>407277</v>
       </c>
       <c r="R10" t="n">
-        <v>7083513.491204341</v>
+        <v>7083681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,19 +1674,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,12 +1691,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>i gammal granskog på frisk mark</t>
+          <t>i gransumpskog nära bäck</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på granlåga ca 30 cm i diameter</t>
+          <t>på ved på högstubbe av björk ca 30 cm i diameter</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1849,15 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96785754</v>
+        <v>96785768</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,21 +1730,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2080</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1892,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406690.0686645505</v>
+        <v>407339</v>
       </c>
       <c r="R11" t="n">
-        <v>7083361.348371542</v>
+        <v>7083647</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1925,19 +1790,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,12 +1807,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>i gammal granskog intill å</t>
+          <t>i gammal granskog på frisk mark</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>på död gran ca 35 cm i diameter</t>
+          <t>på bark på död rönn ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -1980,37 +1835,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96785768</v>
+        <v>96785757</v>
       </c>
       <c r="B12" t="n">
-        <v>78437</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2080</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2023,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407339.4663186476</v>
+        <v>406690</v>
       </c>
       <c r="R12" t="n">
-        <v>7083646.478051158</v>
+        <v>7083362</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2056,19 +1906,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,12 +1923,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>i gammal granskog på frisk mark</t>
+          <t>i gammal granskog intill å</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>på bark på död rönn ca 25 cm i diameter</t>
+          <t>på kvistar på levande gran</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2111,37 +1951,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96785762</v>
+        <v>96785766</v>
       </c>
       <c r="B13" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2154,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407276.8817177833</v>
+        <v>407339</v>
       </c>
       <c r="R13" t="n">
-        <v>7083680.971584482</v>
+        <v>7083647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2187,19 +2022,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,12 +2039,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>i gransumpskog nära bäck</t>
+          <t>i gammal granskog på frisk mark</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>på ved på högstubbe av björk ca 30 cm i diameter</t>
+          <t>på bark på död rönn ca 25 cm i diameter</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2242,37 +2067,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96785763</v>
+        <v>96785758</v>
       </c>
       <c r="B14" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2285,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407276.8817177833</v>
+        <v>406690</v>
       </c>
       <c r="R14" t="n">
-        <v>7083680.971584482</v>
+        <v>7083362</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2318,19 +2133,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2345,12 +2150,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>i gransumpskog nära bäck</t>
+          <t>i gammal granskog intill å</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>på ved på högstubbe av björk ca 30 cm i diameter</t>
+          <t>på kvistar på levande gran</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2370,137 +2175,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>96785757</v>
-      </c>
-      <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Mellan Edefjället och Sösjöån, mellan Sösjön och Torrön, ca 15 km nordos..., Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>406690.0686645505</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7083361.348371542</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>i gammal granskog intill å</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>på kvistar på levande gran</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58223-2021 artfynd.xlsx
+++ b/artfynd/A 58223-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785762</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785764</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785759</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785761</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785756</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785763</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785766</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2175,8 +2240,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>